--- a/artfynd/A 36939-2025 artfynd.xlsx
+++ b/artfynd/A 36939-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135778316</v>
       </c>
       <c r="B2" t="n">
-        <v>57838</v>
+        <v>57840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36939-2025 artfynd.xlsx
+++ b/artfynd/A 36939-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135778316</v>
       </c>
       <c r="B2" t="n">
-        <v>57840</v>
+        <v>57841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36939-2025 artfynd.xlsx
+++ b/artfynd/A 36939-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135778316</v>
       </c>
       <c r="B2" t="n">
-        <v>57841</v>
+        <v>57845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36939-2025 artfynd.xlsx
+++ b/artfynd/A 36939-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135778316</v>
       </c>
       <c r="B2" t="n">
-        <v>57845</v>
+        <v>57846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36939-2025 artfynd.xlsx
+++ b/artfynd/A 36939-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135778316</v>
       </c>
       <c r="B2" t="n">
-        <v>57846</v>
+        <v>57851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
